--- a/artfynd/A 72305-2021 artfynd.xlsx
+++ b/artfynd/A 72305-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 72305-2021 artfynd.xlsx
+++ b/artfynd/A 72305-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5034208</v>
+        <v>15966914</v>
       </c>
       <c r="B2" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,19 +713,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Södertorp, Upl</t>
+          <t>Södertorp SO 450 m, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>684465.2839236599</v>
+        <v>684487</v>
       </c>
       <c r="R2" t="n">
-        <v>6627891.885475997</v>
+        <v>6627875</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-12-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-12-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Örtrik gallrad granskog på finsediment, f d åker eller ängsmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,19 +791,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15966914</v>
+        <v>15966921</v>
       </c>
       <c r="B3" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -836,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -851,14 +836,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Södertorp SO 450 m, Upl</t>
+          <t>Södertorp SO 500 m, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>684486.8402690503</v>
+        <v>684526</v>
       </c>
       <c r="R3" t="n">
-        <v>6627875.284419198</v>
+        <v>6627915</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,19 +873,9 @@
           <t>2014-06-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-06-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,37 +907,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>15966919</v>
+        <v>15966917</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -972,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>684486.8402690503</v>
+        <v>684487</v>
       </c>
       <c r="R4" t="n">
-        <v>6627875.284419198</v>
+        <v>6627875</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,19 +975,9 @@
           <t>2014-06-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-06-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,15 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>15966916</v>
+        <v>5034208</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,26 +1020,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1092,24 +1047,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Södertorp SO 450 m, Upl</t>
+          <t>Södertorp, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>684486.8402690503</v>
+        <v>684465</v>
       </c>
       <c r="R5" t="n">
-        <v>6627875.284419198</v>
+        <v>6627892</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,22 +1083,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-06-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-12-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-06-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-12-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,7 +1102,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Örtrik gallrad granskog på finsediment, f d åker eller ängsmark</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1180,15 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15966917</v>
+        <v>15966919</v>
       </c>
       <c r="B6" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1220,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>684486.8402690503</v>
+        <v>684487</v>
       </c>
       <c r="R6" t="n">
-        <v>6627875.284419198</v>
+        <v>6627875</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,19 +1188,9 @@
           <t>2014-06-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-06-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,6 +1219,122 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>15966916</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Södertorp SO 450 m, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>684487</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6627875</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rimbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Örtrik gallrad granskog på finsediment, f d åker eller ängsmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 72305-2021 artfynd.xlsx
+++ b/artfynd/A 72305-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15966914</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15966921</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15966917</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5034208</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15966919</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1335,8 +1365,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15966916</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>